--- a/output/2026-10-13/enriched_analysis.xlsx
+++ b/output/2026-10-13/enriched_analysis.xlsx
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.251</v>
+        <v>2.253</v>
       </c>
       <c r="W2" t="n">
-        <v>2799</v>
+        <v>2797</v>
       </c>
       <c r="X2" t="n">
         <v>21.9</v>
@@ -1396,7 +1396,7 @@
         <v>0.044</v>
       </c>
       <c r="W4" t="n">
-        <v>3018</v>
+        <v>3015</v>
       </c>
       <c r="X4" t="n">
         <v>10.4</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.533</v>
+        <v>0.529</v>
       </c>
       <c r="W5" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="X5" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="Y5" t="n">
         <v>19</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.192</v>
+        <v>1.188</v>
       </c>
       <c r="W7" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="X7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Y7" t="n">
         <v>22</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="W8" t="n">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="X8" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Y8" t="n">
         <v>7</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.167</v>
+        <v>1.173</v>
       </c>
       <c r="W9" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X9" t="n">
-        <v>7.3</v>
+        <v>7.26</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2749,7 +2749,7 @@
         <v>-5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>67.16</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>7.21</v>
@@ -2786,7 +2786,7 @@
         <v>0.047</v>
       </c>
       <c r="W10" t="n">
-        <v>15191</v>
+        <v>15201</v>
       </c>
       <c r="X10" t="n">
         <v>38.7</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.341</v>
+        <v>2.346</v>
       </c>
       <c r="W11" t="n">
-        <v>2507</v>
+        <v>2502</v>
       </c>
       <c r="X11" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y11" t="n">
         <v>6</v>
@@ -3250,10 +3250,10 @@
         <v>0.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="X12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Y12" t="n">
         <v>55</v>
@@ -3482,10 +3482,10 @@
         <v>0.065</v>
       </c>
       <c r="W13" t="n">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="X13" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="X14" t="n">
         <v>20.9</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.172</v>
+        <v>0.166</v>
       </c>
       <c r="W16" t="n">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="X16" t="n">
-        <v>54</v>
+        <v>55.6</v>
       </c>
       <c r="Y16" t="n">
         <v>3</v>
@@ -4371,7 +4371,7 @@
         <v>-25</v>
       </c>
       <c r="L17" t="n">
-        <v>74.59</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
@@ -4408,10 +4408,10 @@
         <v>0.068</v>
       </c>
       <c r="W17" t="n">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="X17" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="Y17" t="n">
         <v>20</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3.06</v>
+        <v>3.051</v>
       </c>
       <c r="W18" t="n">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="X18" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
         <v>30</v>
@@ -5096,7 +5096,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>54843</v>
+        <v>54825</v>
       </c>
       <c r="X20" t="n">
         <v>46.4</v>
@@ -5328,10 +5328,10 @@
         <v>0.09</v>
       </c>
       <c r="W21" t="n">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="X21" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="Y21" t="n">
         <v>-5</v>
@@ -5523,7 +5523,7 @@
         <v>32.3</v>
       </c>
       <c r="L22" t="n">
-        <v>71.22</v>
+        <v>71.36</v>
       </c>
       <c r="M22" t="n">
         <v>0.86</v>
@@ -5560,7 +5560,7 @@
         <v>0.1</v>
       </c>
       <c r="W22" t="n">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="X22" t="n">
         <v>37.5</v>
@@ -5789,7 +5789,7 @@
         <v>186</v>
       </c>
       <c r="X23" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="Y23" t="n">
         <v>31</v>
@@ -6011,13 +6011,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.303</v>
+        <v>0.318</v>
       </c>
       <c r="W24" t="n">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="X24" t="n">
-        <v>25.3</v>
+        <v>24.1</v>
       </c>
       <c r="Y24" t="n">
         <v>12</v>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.41</v>
+        <v>0.409</v>
       </c>
       <c r="W25" t="n">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="X25" t="n">
         <v>48.9</v>
@@ -6478,10 +6478,10 @@
         <v>0.26</v>
       </c>
       <c r="W26" t="n">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="X26" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Y26" t="n">
         <v>9</v>
@@ -6710,7 +6710,7 @@
         <v>0.127</v>
       </c>
       <c r="W27" t="n">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="X27" t="n">
         <v>13.9</v>
@@ -6945,7 +6945,7 @@
         <v>380</v>
       </c>
       <c r="X28" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="Y28" t="n">
         <v>21</v>
@@ -7174,10 +7174,10 @@
         <v>0.042</v>
       </c>
       <c r="W29" t="n">
-        <v>1666</v>
+        <v>1662</v>
       </c>
       <c r="X29" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Y29" t="n">
         <v>10</v>
@@ -7870,7 +7870,7 @@
         <v>0.831</v>
       </c>
       <c r="W32" t="n">
-        <v>3804</v>
+        <v>3801</v>
       </c>
       <c r="X32" t="n">
         <v>26.6</v>
@@ -8330,7 +8330,7 @@
         <v>0.237</v>
       </c>
       <c r="W34" t="n">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="X34" t="n">
         <v>17.8</v>
@@ -8562,7 +8562,7 @@
         <v>0.043</v>
       </c>
       <c r="W35" t="n">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="X35" t="n">
         <v>18.6</v>
@@ -8791,13 +8791,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.376</v>
+        <v>0.371</v>
       </c>
       <c r="W36" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="X36" t="n">
-        <v>92.2</v>
+        <v>93.2</v>
       </c>
       <c r="Y36" t="n">
         <v>246</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5361</v>
+        <v>5355</v>
       </c>
       <c r="X38" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4051</v>
+        <v>4064</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9711,13 +9711,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="W40" t="n">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="X40" t="n">
-        <v>8.01</v>
+        <v>7.95</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -9905,7 +9905,7 @@
         <v>14.9</v>
       </c>
       <c r="L41" t="n">
-        <v>68.34</v>
+        <v>68.52</v>
       </c>
       <c r="M41" t="n">
         <v>0.2</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="W42" t="n">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="X42" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="Y42" t="n">
         <v>-8</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="W43" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="X43" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="W44" t="n">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3742</v>
+        <v>3739</v>
       </c>
       <c r="X45" t="n">
-        <v>84.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11100,7 +11100,7 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4868</v>
+        <v>4863</v>
       </c>
       <c r="X46" t="n">
         <v>12.6</v>
@@ -11328,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103386</v>
+        <v>103284</v>
       </c>
       <c r="X47" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.239</v>
+        <v>0.235</v>
       </c>
       <c r="W48" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="X48" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>
@@ -12087,7 +12087,7 @@
         <v>-5.9</v>
       </c>
       <c r="F10" t="n">
-        <v>67.16</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>7.21</v>
@@ -12332,7 +12332,7 @@
         <v>-25</v>
       </c>
       <c r="F17" t="n">
-        <v>74.59</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.11</v>
@@ -12507,7 +12507,7 @@
         <v>32.3</v>
       </c>
       <c r="F22" t="n">
-        <v>71.22</v>
+        <v>71.36</v>
       </c>
       <c r="G22" t="n">
         <v>0.86</v>
@@ -13172,7 +13172,7 @@
         <v>14.9</v>
       </c>
       <c r="F41" t="n">
-        <v>68.34</v>
+        <v>68.52</v>
       </c>
       <c r="G41" t="n">
         <v>0.2</v>

--- a/output/2026-10-13/enriched_analysis.xlsx
+++ b/output/2026-10-13/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.253</v>
+        <v>2.282</v>
       </c>
       <c r="W2" t="n">
-        <v>2797</v>
+        <v>2761</v>
       </c>
       <c r="X2" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.869</v>
+        <v>0.839</v>
       </c>
       <c r="W3" t="n">
-        <v>932</v>
+        <v>965</v>
       </c>
       <c r="X3" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="W4" t="n">
-        <v>3015</v>
+        <v>2970</v>
       </c>
       <c r="X4" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.529</v>
+        <v>0.51</v>
       </c>
       <c r="W5" t="n">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="X5" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="Y5" t="n">
         <v>19</v>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.937</v>
+        <v>1.989</v>
       </c>
       <c r="W6" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.188</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="X7" t="n">
         <v>146</v>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="W8" t="n">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="X8" t="n">
-        <v>9.140000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="Y8" t="n">
         <v>7</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.173</v>
+        <v>1.209</v>
       </c>
       <c r="W9" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="X9" t="n">
-        <v>7.26</v>
+        <v>7.05</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="W10" t="n">
-        <v>15201</v>
+        <v>15122</v>
       </c>
       <c r="X10" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.346</v>
+        <v>2.336</v>
       </c>
       <c r="W11" t="n">
-        <v>2502</v>
+        <v>2513</v>
       </c>
       <c r="X11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Y11" t="n">
         <v>6</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="W12" t="n">
-        <v>1660</v>
+        <v>1687</v>
       </c>
       <c r="X12" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="Y12" t="n">
         <v>55</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="W13" t="n">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>2557</v>
+        <v>2524</v>
       </c>
       <c r="X14" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Y14" t="n">
         <v>8</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="W15" t="n">
-        <v>2387</v>
+        <v>2404</v>
       </c>
       <c r="X15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="Y15" t="n">
         <v>-3</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.166</v>
+        <v>0.185</v>
       </c>
       <c r="W16" t="n">
-        <v>666</v>
+        <v>599</v>
       </c>
       <c r="X16" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
         <v>3</v>
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1632</v>
+        <v>1586</v>
       </c>
       <c r="X17" t="n">
-        <v>37.5</v>
+        <v>36.4</v>
       </c>
       <c r="Y17" t="n">
         <v>20</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>3.051</v>
+        <v>3.189</v>
       </c>
       <c r="W18" t="n">
-        <v>645</v>
+        <v>617</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>18.7</v>
       </c>
       <c r="Y18" t="n">
         <v>30</v>
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>1.876</v>
+        <v>1.86</v>
       </c>
       <c r="W19" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
@@ -5096,10 +5096,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>54825</v>
+        <v>55525</v>
       </c>
       <c r="X20" t="n">
-        <v>46.4</v>
+        <v>47</v>
       </c>
       <c r="Y20" t="n">
         <v>5</v>
@@ -5253,12 +5253,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5270,40 +5270,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>210.75</v>
+        <v>90.83</v>
       </c>
       <c r="J21" t="n">
-        <v>232.74</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.4</v>
+        <v>32.3</v>
       </c>
       <c r="L21" t="n">
-        <v>67.13</v>
+        <v>71.36</v>
       </c>
       <c r="M21" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="N21" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -5317,60 +5317,54 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.09</v>
+        <v>0.101</v>
       </c>
       <c r="W21" t="n">
-        <v>632</v>
+        <v>847</v>
       </c>
       <c r="X21" t="n">
-        <v>10.3</v>
+        <v>37</v>
       </c>
       <c r="Y21" t="n">
-        <v>-5</v>
+        <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>8.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.54</v>
+        <v>0.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>14.8</v>
+        <v>23.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>226.18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>205.72</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>11.1</v>
-      </c>
+        <v>19.61</v>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="n">
-        <v>232.7375571148825</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AK21" t="n">
-        <v>-9.4</v>
+        <v>32.3</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -5379,62 +5373,62 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BA21" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BB21" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BC21" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -5470,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>5704863</v>
+        <v>8585000</v>
       </c>
       <c r="BP21" t="n">
         <v>1</v>
@@ -5485,16 +5479,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5505,98 +5499,104 @@
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
+        <v>13</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>210.75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>232.74</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>67.13</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5704863</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5704863</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>90.83</v>
-      </c>
-      <c r="J22" t="n">
-        <v>68.68000000000001</v>
-      </c>
-      <c r="K22" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>71.36</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8585000</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>8585000</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S22" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="W22" t="n">
+        <v>663</v>
+      </c>
+      <c r="X22" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>29-09-2026</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>862</v>
-      </c>
-      <c r="X22" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>39</v>
-      </c>
       <c r="AB22" t="n">
-        <v>0.55</v>
+        <v>6.54</v>
       </c>
       <c r="AC22" t="n">
-        <v>23.9</v>
+        <v>14.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="AE22" t="b">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>226.18</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>205.72</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>11.1</v>
+      </c>
       <c r="AJ22" t="n">
-        <v>68.68000000000001</v>
+        <v>232.7375571148825</v>
       </c>
       <c r="AK22" t="n">
-        <v>32.3</v>
+        <v>-9.4</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
@@ -5605,62 +5605,62 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BB22" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BC22" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -5696,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>8585000</v>
+        <v>5704863</v>
       </c>
       <c r="BP22" t="n">
         <v>1</v>
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.066</v>
+        <v>1.096</v>
       </c>
       <c r="W23" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="X23" t="n">
-        <v>5.43</v>
+        <v>5.31</v>
       </c>
       <c r="Y23" t="n">
         <v>31</v>
@@ -6011,13 +6011,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.318</v>
+        <v>0.332</v>
       </c>
       <c r="W24" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="X24" t="n">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="Y24" t="n">
         <v>12</v>
@@ -6171,12 +6171,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>13</v>
@@ -6200,28 +6200,28 @@
         <v>-1</v>
       </c>
       <c r="I25" t="n">
-        <v>520.6</v>
+        <v>98.23</v>
       </c>
       <c r="J25" t="n">
-        <v>638.11</v>
+        <v>96.03</v>
       </c>
       <c r="K25" t="n">
-        <v>-18.4</v>
+        <v>2.3</v>
       </c>
       <c r="L25" t="n">
-        <v>64.68000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="M25" t="n">
-        <v>3.93</v>
+        <v>2.6</v>
       </c>
       <c r="N25" t="n">
-        <v>39342571</v>
+        <v>26023230</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>39342571</v>
+        <v>26023230</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -6235,60 +6235,60 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.409</v>
+        <v>0.263</v>
       </c>
       <c r="W25" t="n">
-        <v>961</v>
+        <v>991</v>
       </c>
       <c r="X25" t="n">
-        <v>48.9</v>
+        <v>27</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.11</v>
+        <v>18.68</v>
       </c>
       <c r="AA25" t="n">
-        <v>23</v>
+        <v>-36</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.58</v>
+        <v>6.83</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>-110</v>
+        <v>4.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>593.5700000000001</v>
+        <v>89.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>519.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AI25" t="n">
-        <v>9.5</v>
+        <v>6.9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>638.108361041278</v>
+        <v>96.02667896678967</v>
       </c>
       <c r="AK25" t="n">
-        <v>-18.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -6307,52 +6307,52 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AW25" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="AX25" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>6202680</v>
       </c>
       <c r="BA25" t="n">
-        <v>17574151</v>
+        <v>26023230</v>
       </c>
       <c r="BB25" t="n">
-        <v>39000555</v>
+        <v>26023230</v>
       </c>
       <c r="BC25" t="n">
-        <v>39342571</v>
+        <v>26023230</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6388,10 +6388,10 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>17574151</v>
+        <v>26023230</v>
       </c>
       <c r="BP25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ25" t="n">
         <v>0</v>
@@ -6403,16 +6403,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>13</v>
@@ -6432,28 +6432,28 @@
         <v>-1</v>
       </c>
       <c r="I26" t="n">
-        <v>98.23</v>
+        <v>520.6</v>
       </c>
       <c r="J26" t="n">
-        <v>96.03</v>
+        <v>638.11</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>-18.4</v>
       </c>
       <c r="L26" t="n">
-        <v>71.89</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6</v>
+        <v>3.93</v>
       </c>
       <c r="N26" t="n">
-        <v>26023230</v>
+        <v>39342571</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>26023230</v>
+        <v>39342571</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -6467,60 +6467,60 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.26</v>
+        <v>0.369</v>
       </c>
       <c r="W26" t="n">
-        <v>1002</v>
+        <v>1065</v>
       </c>
       <c r="X26" t="n">
-        <v>27.3</v>
+        <v>54.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.68</v>
+        <v>-0.11</v>
       </c>
       <c r="AA26" t="n">
-        <v>-36</v>
+        <v>23</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.85</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.83</v>
+        <v>1.58</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>4.02</v>
+        <v>-110</v>
       </c>
       <c r="AG26" t="n">
-        <v>89.36</v>
+        <v>593.5700000000001</v>
       </c>
       <c r="AH26" t="n">
-        <v>99.90000000000001</v>
+        <v>519.2</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>96.02667896678967</v>
+        <v>638.108361041278</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.3</v>
+        <v>-18.4</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -6539,52 +6539,52 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="AQ26" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>11</v>
       </c>
-      <c r="AR26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3</v>
-      </c>
       <c r="AW26" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="AX26" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6202680</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>26023230</v>
+        <v>17574151</v>
       </c>
       <c r="BB26" t="n">
-        <v>26023230</v>
+        <v>39000555</v>
       </c>
       <c r="BC26" t="n">
-        <v>26023230</v>
+        <v>39342571</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6620,10 +6620,10 @@
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>26023230</v>
+        <v>17574151</v>
       </c>
       <c r="BP26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ26" t="n">
         <v>0</v>
@@ -6707,13 +6707,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="W27" t="n">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="X27" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="Y27" t="n">
         <v>-1</v>
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="W28" t="n">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="X28" t="n">
-        <v>35.3</v>
+        <v>35.8</v>
       </c>
       <c r="Y28" t="n">
         <v>21</v>
@@ -7174,7 +7174,7 @@
         <v>0.042</v>
       </c>
       <c r="W29" t="n">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="X29" t="n">
         <v>21.7</v>
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.514</v>
+        <v>0.504</v>
       </c>
       <c r="W30" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="X30" t="n">
-        <v>36.2</v>
+        <v>36.9</v>
       </c>
       <c r="Y30" t="n">
         <v>-44</v>
@@ -7563,16 +7563,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7580,40 +7580,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H31" t="n">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="I31" t="n">
-        <v>24.08</v>
+        <v>443.25</v>
       </c>
       <c r="J31" t="n">
-        <v>27.53</v>
+        <v>349.57</v>
       </c>
       <c r="K31" t="n">
-        <v>-12.5</v>
+        <v>26.8</v>
       </c>
       <c r="L31" t="n">
-        <v>61.81</v>
+        <v>70.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0.65</v>
+        <v>31.6</v>
       </c>
       <c r="N31" t="n">
-        <v>6470400</v>
+        <v>315995536</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>6470400</v>
+        <v>315995536</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -7627,7 +7627,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -7635,52 +7635,52 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.254</v>
+        <v>0.826</v>
       </c>
       <c r="W31" t="n">
-        <v>255</v>
+        <v>3825</v>
       </c>
       <c r="X31" t="n">
-        <v>13.4</v>
+        <v>26.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.79</v>
+        <v>127</v>
       </c>
       <c r="AA31" t="n">
-        <v>-30</v>
+        <v>-14</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.21</v>
+        <v>6.41</v>
       </c>
       <c r="AC31" t="n">
-        <v>18</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.32</v>
+        <v>1.05</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.83</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>27.2</v>
+        <v>442.58</v>
       </c>
       <c r="AH31" t="n">
-        <v>31.5</v>
+        <v>433.55</v>
       </c>
       <c r="AI31" t="n">
-        <v>-16.5</v>
+        <v>6.8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>27.53361702127659</v>
+        <v>349.5746258337085</v>
       </c>
       <c r="AK31" t="n">
-        <v>-12.5</v>
+        <v>26.8</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AR31" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AS31" t="n">
         <v>13</v>
@@ -7720,31 +7720,31 @@
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
         <v>6</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1581650</v>
+        <v>464</v>
       </c>
       <c r="BA31" t="n">
-        <v>4267650</v>
+        <v>213764633</v>
       </c>
       <c r="BB31" t="n">
-        <v>6470400</v>
+        <v>213764633</v>
       </c>
       <c r="BC31" t="n">
-        <v>6470400</v>
+        <v>315995536</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
@@ -7780,7 +7780,7 @@
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>4267650</v>
+        <v>213764633</v>
       </c>
       <c r="BP31" t="n">
         <v>1</v>
@@ -7795,12 +7795,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -7812,107 +7812,103 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="J32" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>69.12</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N32" t="n">
+        <v>23479616</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>23479616</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
         <v>25</v>
       </c>
-      <c r="H32" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I32" t="n">
-        <v>443.25</v>
-      </c>
-      <c r="J32" t="n">
-        <v>349.57</v>
-      </c>
-      <c r="K32" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="L32" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="M32" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="N32" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>11</v>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.831</v>
+        <v>0.671</v>
       </c>
       <c r="W32" t="n">
-        <v>3801</v>
+        <v>350</v>
       </c>
       <c r="X32" t="n">
-        <v>26.6</v>
+        <v>1129</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>127</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>-14</v>
+        <v>-98</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.41</v>
+        <v>0.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.890000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>21</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="n">
-        <v>442.58</v>
+        <v>12.8</v>
       </c>
       <c r="AH32" t="n">
-        <v>433.55</v>
+        <v>12.93</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>349.5746258337085</v>
+        <v>12.85608234597773</v>
       </c>
       <c r="AK32" t="n">
-        <v>26.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
@@ -7926,57 +7922,57 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AR32" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="AS32" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW32" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AX32" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>213764633</v>
+        <v>2496337</v>
       </c>
       <c r="BB32" t="n">
-        <v>213764633</v>
+        <v>16559572</v>
       </c>
       <c r="BC32" t="n">
-        <v>315995536</v>
+        <v>23479616</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8012,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>213764633</v>
+        <v>2496337</v>
       </c>
       <c r="BP32" t="n">
         <v>1</v>
@@ -8027,16 +8023,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8044,40 +8040,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>-1</v>
       </c>
       <c r="I33" t="n">
-        <v>12.76</v>
+        <v>24.08</v>
       </c>
       <c r="J33" t="n">
-        <v>12.86</v>
+        <v>27.53</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.8</v>
+        <v>-12.5</v>
       </c>
       <c r="L33" t="n">
-        <v>69.12</v>
+        <v>61.81</v>
       </c>
       <c r="M33" t="n">
-        <v>2.35</v>
+        <v>0.65</v>
       </c>
       <c r="N33" t="n">
-        <v>23479616</v>
+        <v>6470400</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>23479616</v>
+        <v>6470400</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -8091,56 +8087,60 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.652</v>
+        <v>0.249</v>
       </c>
       <c r="W33" t="n">
-        <v>360</v>
+        <v>260</v>
       </c>
       <c r="X33" t="n">
-        <v>1162</v>
+        <v>13.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>-61</v>
-      </c>
-      <c r="Z33" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.79</v>
+      </c>
       <c r="AA33" t="n">
-        <v>-98</v>
+        <v>-30</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.46</v>
+        <v>18</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.83</v>
+      </c>
       <c r="AG33" t="n">
-        <v>12.8</v>
+        <v>27.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>12.93</v>
+        <v>31.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.3</v>
+        <v>-16.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>12.85608234597773</v>
+        <v>27.53361702127659</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.7</v>
+        <v>-12.5</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -8159,52 +8159,52 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AR33" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="AS33" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW33" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AX33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1581650</v>
       </c>
       <c r="BA33" t="n">
-        <v>2496337</v>
+        <v>4267650</v>
       </c>
       <c r="BB33" t="n">
-        <v>16559572</v>
+        <v>6470400</v>
       </c>
       <c r="BC33" t="n">
-        <v>23479616</v>
+        <v>6470400</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>2496337</v>
+        <v>4267650</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
@@ -8327,13 +8327,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.237</v>
+        <v>0.229</v>
       </c>
       <c r="W34" t="n">
-        <v>1686</v>
+        <v>1740</v>
       </c>
       <c r="X34" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="Y34" t="n">
         <v>-3</v>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="W35" t="n">
-        <v>3140</v>
+        <v>3218</v>
       </c>
       <c r="X35" t="n">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y35" t="n">
         <v>-4</v>
@@ -8791,13 +8791,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="W36" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="X36" t="n">
-        <v>93.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y36" t="n">
         <v>246</v>
@@ -9252,10 +9252,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>5355</v>
+        <v>5219</v>
       </c>
       <c r="X38" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="Y38" t="n">
         <v>26</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4064</v>
+        <v>4019</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9639,12 +9639,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -9656,10 +9656,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
         <v>25</v>
@@ -9668,28 +9668,28 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>25.88</v>
+        <v>27.07</v>
       </c>
       <c r="J40" t="n">
-        <v>21.01</v>
+        <v>23.55</v>
       </c>
       <c r="K40" t="n">
-        <v>23.2</v>
+        <v>14.9</v>
       </c>
       <c r="L40" t="n">
-        <v>70.87</v>
+        <v>68.52</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N40" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -9703,90 +9703,94 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.101</v>
+        <v>0.144</v>
       </c>
       <c r="W40" t="n">
-        <v>492</v>
+        <v>140</v>
       </c>
       <c r="X40" t="n">
-        <v>7.95</v>
+        <v>32.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z40" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.17</v>
+      </c>
       <c r="AA40" t="n">
-        <v>391</v>
+        <v>7</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="AC40" t="n">
-        <v>19.9</v>
+        <v>8.76</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
+      <c r="AF40" t="n">
+        <v>14.87</v>
+      </c>
       <c r="AG40" t="n">
-        <v>20.42</v>
+        <v>24.91</v>
       </c>
       <c r="AH40" t="n">
-        <v>15.91</v>
+        <v>22.86</v>
       </c>
       <c r="AI40" t="n">
-        <v>89.90000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ40" t="n">
-        <v>21.00741139152052</v>
+        <v>23.5472893358377</v>
       </c>
       <c r="AK40" t="n">
-        <v>23.2</v>
+        <v>15</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ40" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AR40" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AS40" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AT40" t="n">
         <v>0</v>
@@ -9795,13 +9799,13 @@
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW40" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AX40" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -9810,13 +9814,13 @@
         <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1308280</v>
       </c>
       <c r="BB40" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="BC40" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
@@ -9852,10 +9856,10 @@
         <v>0</v>
       </c>
       <c r="BO40" t="n">
-        <v>0</v>
+        <v>1308280</v>
       </c>
       <c r="BP40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BQ40" t="n">
         <v>0</v>
@@ -9867,16 +9871,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9884,10 +9888,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
         <v>25</v>
@@ -9896,28 +9900,28 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>27.07</v>
+        <v>25.88</v>
       </c>
       <c r="J41" t="n">
-        <v>23.55</v>
+        <v>21.01</v>
       </c>
       <c r="K41" t="n">
-        <v>14.9</v>
+        <v>23.2</v>
       </c>
       <c r="L41" t="n">
-        <v>68.52</v>
+        <v>70.87</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -9931,94 +9935,90 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.145</v>
+        <v>0.099</v>
       </c>
       <c r="W41" t="n">
-        <v>139</v>
+        <v>499</v>
       </c>
       <c r="X41" t="n">
-        <v>32</v>
+        <v>8.06</v>
       </c>
       <c r="Y41" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.17</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.49</v>
+        <v>1.03</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.76</v>
+        <v>19.9</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="n">
-        <v>14.87</v>
-      </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="n">
-        <v>24.91</v>
+        <v>20.42</v>
       </c>
       <c r="AH41" t="n">
-        <v>22.86</v>
+        <v>15.91</v>
       </c>
       <c r="AI41" t="n">
-        <v>9.199999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AJ41" t="n">
-        <v>23.5472893358377</v>
+        <v>21.00741139152052</v>
       </c>
       <c r="AK41" t="n">
-        <v>15</v>
+        <v>23.2</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AQ41" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR41" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AS41" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AT41" t="n">
         <v>0</v>
@@ -10027,13 +10027,13 @@
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AX41" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
@@ -10042,13 +10042,13 @@
         <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1308280</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="BC41" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="BO41" t="n">
-        <v>1308280</v>
+        <v>0</v>
       </c>
       <c r="BP41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BQ41" t="n">
         <v>0</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="W42" t="n">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="X42" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="Y42" t="n">
         <v>-8</v>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -10403,13 +10403,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.095</v>
+        <v>0.1</v>
       </c>
       <c r="W43" t="n">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="X43" t="n">
-        <v>28.9</v>
+        <v>27.4</v>
       </c>
       <c r="Y43" t="n">
         <v>24</v>
@@ -10638,7 +10638,7 @@
         <v>0.052</v>
       </c>
       <c r="W44" t="n">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="n">
@@ -10868,10 +10868,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3739</v>
+        <v>3827</v>
       </c>
       <c r="X45" t="n">
-        <v>84.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y45" t="n">
         <v>42</v>
@@ -11100,7 +11100,7 @@
         <v>0.006</v>
       </c>
       <c r="W46" t="n">
-        <v>4863</v>
+        <v>4885</v>
       </c>
       <c r="X46" t="n">
         <v>12.6</v>
@@ -11328,10 +11328,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>103284</v>
+        <v>104942</v>
       </c>
       <c r="X47" t="n">
-        <v>29.7</v>
+        <v>30.3</v>
       </c>
       <c r="Y47" t="n">
         <v>18</v>
@@ -11563,7 +11563,7 @@
         <v>191</v>
       </c>
       <c r="X48" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>
@@ -12454,70 +12454,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>210.75</v>
+        <v>90.83</v>
       </c>
       <c r="D21" t="n">
-        <v>232.74</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.4</v>
+        <v>32.3</v>
       </c>
       <c r="F21" t="n">
-        <v>67.13</v>
+        <v>71.36</v>
       </c>
       <c r="G21" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>90.83</v>
+        <v>210.75</v>
       </c>
       <c r="D22" t="n">
-        <v>68.68000000000001</v>
+        <v>232.74</v>
       </c>
       <c r="E22" t="n">
-        <v>32.3</v>
+        <v>-9.4</v>
       </c>
       <c r="F22" t="n">
-        <v>71.36</v>
+        <v>67.13</v>
       </c>
       <c r="G22" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -12594,70 +12594,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>520.6</v>
+        <v>98.23</v>
       </c>
       <c r="D25" t="n">
-        <v>638.11</v>
+        <v>96.03</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.4</v>
+        <v>2.3</v>
       </c>
       <c r="F25" t="n">
-        <v>64.68000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="G25" t="n">
-        <v>3.93</v>
+        <v>2.6</v>
       </c>
       <c r="H25" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>98.23</v>
+        <v>520.6</v>
       </c>
       <c r="D26" t="n">
-        <v>96.03</v>
+        <v>638.11</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3</v>
+        <v>-18.4</v>
       </c>
       <c r="F26" t="n">
-        <v>71.89</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>2.6</v>
+        <v>3.93</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
@@ -12804,31 +12804,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.08</v>
+        <v>443.25</v>
       </c>
       <c r="D31" t="n">
-        <v>27.53</v>
+        <v>349.57</v>
       </c>
       <c r="E31" t="n">
-        <v>-12.5</v>
+        <v>26.8</v>
       </c>
       <c r="F31" t="n">
-        <v>61.81</v>
+        <v>70.55</v>
       </c>
       <c r="G31" t="n">
-        <v>0.65</v>
+        <v>31.6</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -12839,70 +12839,70 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>443.25</v>
+        <v>12.76</v>
       </c>
       <c r="D32" t="n">
-        <v>349.57</v>
+        <v>12.86</v>
       </c>
       <c r="E32" t="n">
-        <v>26.8</v>
+        <v>-0.8</v>
       </c>
       <c r="F32" t="n">
-        <v>70.55</v>
+        <v>69.12</v>
       </c>
       <c r="G32" t="n">
-        <v>31.6</v>
+        <v>2.35</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12.76</v>
+        <v>24.08</v>
       </c>
       <c r="D33" t="n">
-        <v>12.86</v>
+        <v>27.53</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8</v>
+        <v>-12.5</v>
       </c>
       <c r="F33" t="n">
-        <v>69.12</v>
+        <v>61.81</v>
       </c>
       <c r="G33" t="n">
-        <v>2.35</v>
+        <v>0.65</v>
       </c>
       <c r="H33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
@@ -13119,70 +13119,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>25.88</v>
+        <v>27.07</v>
       </c>
       <c r="D40" t="n">
-        <v>21.01</v>
+        <v>23.55</v>
       </c>
       <c r="E40" t="n">
-        <v>23.2</v>
+        <v>14.9</v>
       </c>
       <c r="F40" t="n">
-        <v>70.87</v>
+        <v>68.52</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27.07</v>
+        <v>25.88</v>
       </c>
       <c r="D41" t="n">
-        <v>23.55</v>
+        <v>21.01</v>
       </c>
       <c r="E41" t="n">
-        <v>14.9</v>
+        <v>23.2</v>
       </c>
       <c r="F41" t="n">
-        <v>68.52</v>
+        <v>70.87</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-13/enriched_analysis.xlsx
+++ b/output/2026-10-13/enriched_analysis.xlsx
@@ -1396,10 +1396,10 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3424</v>
+        <v>3406</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="Y4" t="n">
         <v>18</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.025</v>
+        <v>1.033</v>
       </c>
       <c r="W6" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="X6" t="n">
-        <v>88.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="Y6" t="n">
         <v>111</v>
@@ -3948,7 +3948,7 @@
         <v>0.049</v>
       </c>
       <c r="W15" t="n">
-        <v>1696</v>
+        <v>1690</v>
       </c>
       <c r="X15" t="n">
         <v>22.8</v>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="W20" t="n">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="X20" t="n">
         <v>20.9</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>2522</v>
+        <v>2529</v>
       </c>
       <c r="X21" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="W23" t="n">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="X23" t="n">
         <v>13.1</v>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.319</v>
+        <v>0.32</v>
       </c>
       <c r="W26" t="n">
-        <v>59611</v>
+        <v>59479</v>
       </c>
       <c r="X26" t="n">
         <v>22.2</v>
@@ -7874,10 +7874,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>55719</v>
+        <v>55608</v>
       </c>
       <c r="X32" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="Y32" t="n">
         <v>5</v>
@@ -8103,13 +8103,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="X33" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="Y33" t="n">
         <v>-5</v>
@@ -9283,7 +9283,7 @@
         <v>1.58</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
@@ -11573,10 +11573,10 @@
         </is>
       </c>
       <c r="V48" t="n">
-        <v>4.659</v>
+        <v>4.601</v>
       </c>
       <c r="W48" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="n">
@@ -12499,13 +12499,13 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>0.66</v>
+        <v>0.671</v>
       </c>
       <c r="W52" t="n">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="X52" t="n">
-        <v>1147</v>
+        <v>1129</v>
       </c>
       <c r="Y52" t="n">
         <v>-61</v>
@@ -13188,7 +13188,7 @@
         <v>0.231</v>
       </c>
       <c r="W55" t="n">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="X55" t="n">
         <v>18.3</v>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>0.196</v>
+        <v>0.198</v>
       </c>
       <c r="W61" t="n">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="X61" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="Y61" t="n">
         <v>-1</v>
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="V62" t="n">
-        <v>0.48</v>
+        <v>0.482</v>
       </c>
       <c r="W62" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="X62" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="Y62" t="n">
         <v>6</v>
@@ -15429,12 +15429,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -15446,10 +15446,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G65" t="n">
         <v>25</v>
@@ -15458,28 +15458,28 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>27.2</v>
+        <v>25.82</v>
       </c>
       <c r="J65" t="n">
-        <v>23.55</v>
+        <v>21.01</v>
       </c>
       <c r="K65" t="n">
-        <v>15.5</v>
+        <v>22.9</v>
       </c>
       <c r="L65" t="n">
-        <v>68.52</v>
+        <v>70.87</v>
       </c>
       <c r="M65" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="N65" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -15493,94 +15493,90 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>0.145</v>
+        <v>0.1</v>
       </c>
       <c r="W65" t="n">
-        <v>139</v>
+        <v>495</v>
       </c>
       <c r="X65" t="n">
-        <v>32.2</v>
+        <v>8</v>
       </c>
       <c r="Y65" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>3.17</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="n">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.49</v>
+        <v>1.03</v>
       </c>
       <c r="AC65" t="n">
-        <v>8.76</v>
+        <v>19.9</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="n">
-        <v>14.87</v>
-      </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="n">
-        <v>24.97</v>
+        <v>20.54</v>
       </c>
       <c r="AH65" t="n">
-        <v>22.85</v>
+        <v>15.97</v>
       </c>
       <c r="AI65" t="n">
-        <v>13.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AJ65" t="n">
-        <v>23.5472893358377</v>
+        <v>21.00741139152052</v>
       </c>
       <c r="AK65" t="n">
-        <v>15.5</v>
+        <v>22.9</v>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AQ65" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR65" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AS65" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AT65" t="n">
         <v>0</v>
@@ -15589,13 +15585,13 @@
         <v>0</v>
       </c>
       <c r="AV65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AX65" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AY65" t="n">
         <v>0</v>
@@ -15604,13 +15600,13 @@
         <v>0</v>
       </c>
       <c r="BA65" t="n">
-        <v>1308280</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="BC65" t="n">
-        <v>2018403</v>
+        <v>4960333</v>
       </c>
       <c r="BD65" t="n">
         <v>0</v>
@@ -15646,10 +15642,10 @@
         <v>0</v>
       </c>
       <c r="BO65" t="n">
-        <v>1308280</v>
+        <v>0</v>
       </c>
       <c r="BP65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BQ65" t="n">
         <v>0</v>
@@ -15661,16 +15657,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -15678,10 +15674,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
         <v>25</v>
@@ -15690,28 +15686,28 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>25.82</v>
+        <v>27.2</v>
       </c>
       <c r="J66" t="n">
-        <v>21.01</v>
+        <v>23.55</v>
       </c>
       <c r="K66" t="n">
-        <v>22.9</v>
+        <v>15.5</v>
       </c>
       <c r="L66" t="n">
-        <v>70.87</v>
+        <v>68.52</v>
       </c>
       <c r="M66" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N66" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -15725,90 +15721,94 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>0.099</v>
+        <v>0.145</v>
       </c>
       <c r="W66" t="n">
-        <v>503</v>
+        <v>139</v>
       </c>
       <c r="X66" t="n">
-        <v>8.130000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="Y66" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z66" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>3.17</v>
+      </c>
       <c r="AA66" t="n">
-        <v>391</v>
+        <v>7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="AC66" t="n">
-        <v>19.9</v>
+        <v>8.76</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
+      <c r="AF66" t="n">
+        <v>14.87</v>
+      </c>
       <c r="AG66" t="n">
-        <v>20.54</v>
+        <v>24.97</v>
       </c>
       <c r="AH66" t="n">
-        <v>15.97</v>
+        <v>22.85</v>
       </c>
       <c r="AI66" t="n">
-        <v>88.09999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="AJ66" t="n">
-        <v>21.00741139152052</v>
+        <v>23.5472893358377</v>
       </c>
       <c r="AK66" t="n">
-        <v>22.9</v>
+        <v>15.5</v>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ66" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AR66" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AS66" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AT66" t="n">
         <v>0</v>
@@ -15817,13 +15817,13 @@
         <v>0</v>
       </c>
       <c r="AV66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AW66" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AX66" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AY66" t="n">
         <v>0</v>
@@ -15832,13 +15832,13 @@
         <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>1308280</v>
       </c>
       <c r="BB66" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="BC66" t="n">
-        <v>4960333</v>
+        <v>2018403</v>
       </c>
       <c r="BD66" t="n">
         <v>0</v>
@@ -15874,10 +15874,10 @@
         <v>0</v>
       </c>
       <c r="BO66" t="n">
-        <v>0</v>
+        <v>1308280</v>
       </c>
       <c r="BP66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BQ66" t="n">
         <v>0</v>
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>8</v>
@@ -16426,10 +16426,10 @@
         <v>0.1</v>
       </c>
       <c r="W69" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="X69" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="Y69" t="n">
         <v>24</v>
@@ -18728,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>104067</v>
+        <v>104264</v>
       </c>
       <c r="X79" t="n">
         <v>30</v>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="W80" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="n">
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>0.082</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="W82" t="n">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
@@ -21854,70 +21854,70 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>27.2</v>
+        <v>25.82</v>
       </c>
       <c r="D65" t="n">
-        <v>23.55</v>
+        <v>21.01</v>
       </c>
       <c r="E65" t="n">
-        <v>15.5</v>
+        <v>22.9</v>
       </c>
       <c r="F65" t="n">
-        <v>68.52</v>
+        <v>70.87</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H65" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>25.82</v>
+        <v>27.2</v>
       </c>
       <c r="D66" t="n">
-        <v>21.01</v>
+        <v>23.55</v>
       </c>
       <c r="E66" t="n">
-        <v>22.9</v>
+        <v>15.5</v>
       </c>
       <c r="F66" t="n">
-        <v>70.87</v>
+        <v>68.52</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
